--- a/测试用例清单.xlsx
+++ b/测试用例清单.xlsx
@@ -1283,7 +1283,7 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1321,7 +1321,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1511,7 +1511,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2934,8 +2934,16 @@
           <t>detect_mode(data) 返回 timestamp</t>
         </is>
       </c>
-      <c r="K2" s="14" t="n"/>
-      <c r="L2" s="14" t="n"/>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>返回 timestamp</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -2994,8 +3002,16 @@
           <t>图中节点数为 3、边数为 2；序列化结果 nodes 数量为 3、links 数量为 2</t>
         </is>
       </c>
-      <c r="K3" s="14" t="n"/>
-      <c r="L3" s="14" t="n"/>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>节点 3、边 2；nodes 3、links 2</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3051,8 +3067,16 @@
           <t>detect_mode(data) 返回 snapshot</t>
         </is>
       </c>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>返回 snapshot</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M4" s="15" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3104,8 +3128,16 @@
           <t>detect_mode(data) 返回 timestamp</t>
         </is>
       </c>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="14" t="n"/>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>返回 timestamp</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M5" s="15" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3155,8 +3187,16 @@
           <t>detect_mode(data) 返回 snapshot</t>
         </is>
       </c>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>返回 snapshot</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3204,8 +3244,16 @@
           <t>读取内容与输入一致；图中节点数为 10、边数为 9</t>
         </is>
       </c>
-      <c r="K7" s="14" t="n"/>
-      <c r="L7" s="14" t="n"/>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>读取内容与输入一致；节点 10、边 9</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3254,8 +3302,16 @@
           <t>图中节点数、边数均为 20；序列化 nodes 与 links 数量均为 20</t>
         </is>
       </c>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>节点、边、nodes、links 均为 20</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3301,8 +3357,16 @@
           <t>返回空图，节点数为 0、边数为 0；对应 Pytest 用例通过。</t>
         </is>
       </c>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>空图，节点 0、边 0</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3351,8 +3415,16 @@
           <t>图中节点数为 2、边数为 1，边的 timestamp 为 1</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>节点 2、边 1，timestamp 为 1</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3401,8 +3473,16 @@
           <t>序列化 links 数量为 1，且 timestamp 仍为 0</t>
         </is>
       </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>links 数量 1，timestamp 仍为 0</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3448,8 +3528,16 @@
           <t>返回空列表 []</t>
         </is>
       </c>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>返回 []</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3502,8 +3590,16 @@
           <t>图列表长度为 1；图中节点 Solo 数量为 1、边数为 0；序列化 links 为空</t>
         </is>
       </c>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>图列表长度 1；节点 Solo 数量 1、边 0；links 为空</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3553,8 +3649,16 @@
           <t>返回 200；JSON 为 {"path": ["A", "B", "C"]}</t>
         </is>
       </c>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="14" t="n"/>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>200，path 为 A-B-C</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3604,8 +3708,16 @@
           <t>返回 404；JSON error 为“两节点之间不存在有向路径”</t>
         </is>
       </c>
-      <c r="K15" s="14" t="n"/>
-      <c r="L15" s="14" t="n"/>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>404，两节点之间不存在有向路径</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M15" s="14" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3654,8 +3766,16 @@
           <t>返回 404；JSON error 为“当前视图中不存在该节点”</t>
         </is>
       </c>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>404，当前视图中不存在该节点</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
           <t>等价类法</t>
@@ -3705,8 +3825,16 @@
           <t>返回 200；JSON 为 {"path": ["A"]}</t>
         </is>
       </c>
-      <c r="K17" s="14" t="n"/>
-      <c r="L17" s="14" t="n"/>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>200，path 为 A</t>
+        </is>
+      </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3756,8 +3884,16 @@
           <t>返回 200；JSON 为 {"path": ["A", "B"]}</t>
         </is>
       </c>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>200，path 为 A-B</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>
@@ -3807,8 +3943,16 @@
           <t>返回 404；JSON error 为“当前视图中不存在该节点”</t>
         </is>
       </c>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="14" t="n"/>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>404，当前视图中不存在该节点</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
           <t>边界值法</t>

--- a/测试用例清单.xlsx
+++ b/测试用例清单.xlsx
@@ -4473,12 +4473,12 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>仍为启动时的 X/Y/Z</t>
+          <t>节点为 A、B</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400，含 error</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400，含 error</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200，detected_mode=timestamp</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
